--- a/data/trans_dic/IP18A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 18,87</t>
+          <t>6,56; 19,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 17,2</t>
+          <t>5,82; 17,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,53</t>
+          <t>1,36; 13,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,94</t>
+          <t>0,0; 58,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 14,27</t>
+          <t>3,7; 13,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 19,13</t>
+          <t>5,07; 17,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,04</t>
+          <t>2,65; 14,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,14</t>
+          <t>0,0; 29,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 14,01</t>
+          <t>5,86; 13,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 15,24</t>
+          <t>6,73; 15,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,85</t>
+          <t>3,19; 11,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 30,73</t>
+          <t>2,46; 29,54</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,78</t>
+          <t>5,29; 9,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,79</t>
+          <t>7,18; 11,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 13,83</t>
+          <t>8,84; 13,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,83</t>
+          <t>3,18; 13,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,23</t>
+          <t>6,08; 10,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,85</t>
+          <t>8,0; 12,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,33</t>
+          <t>5,96; 10,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,41</t>
+          <t>1,62; 7,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,16</t>
+          <t>6,15; 9,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 11,47</t>
+          <t>8,17; 11,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,43</t>
+          <t>7,99; 11,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,34</t>
+          <t>2,89; 8,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,3</t>
+          <t>6,93; 14,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,04</t>
+          <t>7,32; 15,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,61</t>
+          <t>3,22; 10,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,29</t>
+          <t>0,0; 17,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 14,85</t>
+          <t>6,38; 14,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 13,46</t>
+          <t>5,82; 13,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 16,46</t>
+          <t>7,73; 15,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>0,0; 14,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,2</t>
+          <t>7,49; 13,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 13,38</t>
+          <t>7,67; 13,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,48</t>
+          <t>6,4; 11,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,81</t>
+          <t>0,96; 11,99</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,52</t>
+          <t>6,86; 10,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,86</t>
+          <t>7,97; 11,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,4</t>
+          <t>7,51; 11,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,66</t>
+          <t>3,62; 12,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,07</t>
+          <t>6,62; 10,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,89</t>
+          <t>8,16; 11,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,76</t>
+          <t>7,07; 10,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,47</t>
+          <t>1,93; 7,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,76</t>
+          <t>7,28; 9,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,34</t>
+          <t>8,6; 11,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,46</t>
+          <t>7,84; 10,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,11</t>
+          <t>3,53; 8,14</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9272</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13648</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17338</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7354</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4686; 13782</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5047; 14972</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>743; 7145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3843</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2743; 10233</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3900; 13791</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1645; 9059</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2811</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>8528; 19299</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11015; 24746</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3722; 13261</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>394; 4720</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>26747</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38620</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48148</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32907</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46922</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34652</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>59654</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>85542</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>82800</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7917</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>19702; 34826</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30247; 49719</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38300; 59547</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2104; 8710</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24887; 42308</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>37327; 59708</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25984; 44735</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1475; 7249</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>48060; 72625</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>72474; 101515</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>69422; 97861</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4558; 12933</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17216</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9195</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13810</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15190</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19520</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>30011</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>32406</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28715</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10694; 22769</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11418; 23845</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4915; 15607</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4717</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8927; 20645</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9528; 22540</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13270; 26580</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4591</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>22030; 39207</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24525; 42787</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20756; 37787</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>561; 7006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>51127</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65108</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60248</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70178</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5343</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>103313</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>135286</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118869</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12503</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>41000; 62606</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>52879; 77802</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48061; 73365</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3635; 12644</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>41265; 64874</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>57727; 84675</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>47364; 70654</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2536; 9440</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>88957; 119181</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>117856; 152398</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>102744; 138204</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8178; 18872</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 19,3</t>
+          <t>6,21; 17,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 17,27</t>
+          <t>5,84; 17,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,07</t>
+          <t>1,44; 12,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,71</t>
+          <t>0,0; 53,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,82</t>
+          <t>3,55; 13,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 17,91</t>
+          <t>5,43; 19,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,6</t>
+          <t>2,68; 14,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,79</t>
+          <t>0,0; 32,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 13,27</t>
+          <t>5,76; 13,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,12</t>
+          <t>7,14; 15,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 11,36</t>
+          <t>3,12; 11,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 29,54</t>
+          <t>2,28; 29,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,35</t>
+          <t>5,02; 9,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,81</t>
+          <t>7,17; 11,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,75</t>
+          <t>8,94; 13,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,15</t>
+          <t>3,3; 12,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,34</t>
+          <t>5,97; 10,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,8</t>
+          <t>7,94; 12,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,26</t>
+          <t>6,06; 10,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,94</t>
+          <t>1,58; 7,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,29</t>
+          <t>6,28; 9,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,44</t>
+          <t>8,14; 11,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,26</t>
+          <t>8,09; 11,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 8,21</t>
+          <t>2,87; 8,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,76</t>
+          <t>6,94; 15,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,28</t>
+          <t>7,34; 15,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,22</t>
+          <t>3,36; 10,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,13</t>
+          <t>0,0; 21,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 14,75</t>
+          <t>6,05; 14,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,77</t>
+          <t>5,75; 13,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 15,48</t>
+          <t>7,82; 15,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,85</t>
+          <t>0,0; 14,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,33</t>
+          <t>7,53; 13,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,38</t>
+          <t>7,51; 13,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,65</t>
+          <t>6,46; 11,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 11,99</t>
+          <t>1,6; 11,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,47</t>
+          <t>7,05; 10,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,72</t>
+          <t>8,12; 11,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,46</t>
+          <t>7,65; 11,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,6</t>
+          <t>3,76; 12,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,41</t>
+          <t>6,81; 10,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,98</t>
+          <t>8,22; 11,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,55</t>
+          <t>7,16; 10,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,17</t>
+          <t>1,92; 7,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,76</t>
+          <t>7,33; 9,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,12</t>
+          <t>8,6; 11,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,55</t>
+          <t>7,84; 10,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,14</t>
+          <t>3,33; 8,02</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4686; 13782</t>
+          <t>4436; 12636</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5047; 14972</t>
+          <t>5066; 14759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>743; 7145</t>
+          <t>788; 6823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3843</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2743; 10233</t>
+          <t>2629; 10157</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3900; 13791</t>
+          <t>4179; 14712</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1645; 9059</t>
+          <t>1663; 8844</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2811</t>
+          <t>0; 3090</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8528; 19299</t>
+          <t>8384; 19832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11015; 24746</t>
+          <t>11681; 24944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3722; 13261</t>
+          <t>3645; 12973</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>394; 4720</t>
+          <t>365; 4727</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19702; 34826</t>
+          <t>18701; 34823</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30247; 49719</t>
+          <t>30194; 49406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38300; 59547</t>
+          <t>38697; 60335</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2104; 8710</t>
+          <t>2184; 8412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24887; 42308</t>
+          <t>24420; 42836</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37327; 59708</t>
+          <t>37045; 59145</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25984; 44735</t>
+          <t>26433; 45283</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1475; 7249</t>
+          <t>1441; 6746</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48060; 72625</t>
+          <t>49086; 72388</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72474; 101515</t>
+          <t>72214; 101119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69422; 97861</t>
+          <t>70277; 97956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4558; 12933</t>
+          <t>4520; 13286</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10694; 22769</t>
+          <t>10704; 23419</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11418; 23845</t>
+          <t>11461; 24639</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4915; 15607</t>
+          <t>5129; 15485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 5991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8927; 20645</t>
+          <t>8466; 20560</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9528; 22540</t>
+          <t>9419; 22256</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13270; 26580</t>
+          <t>13428; 27209</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 4505</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22030; 39207</t>
+          <t>22141; 39497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24525; 42787</t>
+          <t>24008; 42763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20756; 37787</t>
+          <t>20957; 37851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>561; 7006</t>
+          <t>933; 6777</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41000; 62606</t>
+          <t>42169; 63698</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52879; 77802</t>
+          <t>53923; 77796</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48061; 73365</t>
+          <t>49014; 74082</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3635; 12644</t>
+          <t>3769; 12784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41265; 64874</t>
+          <t>42429; 63941</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57727; 84675</t>
+          <t>58142; 83651</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47364; 70654</t>
+          <t>47953; 72760</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2536; 9440</t>
+          <t>2529; 10005</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88957; 119181</t>
+          <t>89537; 119611</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117856; 152398</t>
+          <t>117903; 153264</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102744; 138204</t>
+          <t>102758; 135141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8178; 18872</t>
+          <t>7716; 18602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11,46%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,7%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,31%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 17,7</t>
+          <t>3,55; 14,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 17,02</t>
+          <t>5,02; 19,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,48</t>
+          <t>2,94; 16,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,65</t>
+          <t>0,0; 35,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,71</t>
+          <t>6,38; 18,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 19,11</t>
+          <t>5,87; 17,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,25</t>
+          <t>1,36; 12,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,75</t>
+          <t>0,0; 58,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 13,63</t>
+          <t>5,95; 14,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 15,24</t>
+          <t>6,97; 15,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,11</t>
+          <t>3,13; 10,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 29,58</t>
+          <t>2,35; 28,76</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,35</t>
+          <t>6,11; 10,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,73</t>
+          <t>7,87; 12,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,93</t>
+          <t>5,91; 10,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,7</t>
+          <t>1,25; 6,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,47</t>
+          <t>5,25; 9,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 12,68</t>
+          <t>7,18; 11,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,39</t>
+          <t>8,93; 13,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,39</t>
+          <t>2,92; 13,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,26</t>
+          <t>6,23; 9,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,4</t>
+          <t>8,0; 11,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,27</t>
+          <t>7,98; 11,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,44</t>
+          <t>2,8; 8,04</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,02%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 15,18</t>
+          <t>6,21; 14,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,79</t>
+          <t>6,08; 13,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 10,14</t>
+          <t>7,79; 16,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,76</t>
+          <t>0,0; 17,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,69</t>
+          <t>6,81; 15,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 13,6</t>
+          <t>7,46; 16,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 15,85</t>
+          <t>3,38; 9,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,57</t>
+          <t>0,0; 19,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 13,42</t>
+          <t>7,4; 13,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,37</t>
+          <t>7,57; 13,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,67</t>
+          <t>6,38; 11,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 11,6</t>
+          <t>1,57; 14,05</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,65</t>
+          <t>6,64; 10,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,72</t>
+          <t>8,3; 11,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,57</t>
+          <t>6,86; 10,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,74</t>
+          <t>1,87; 7,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,26</t>
+          <t>6,81; 10,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,83</t>
+          <t>7,98; 11,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,86</t>
+          <t>7,76; 11,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,6</t>
+          <t>3,45; 12,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 9,79</t>
+          <t>7,25; 9,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,18</t>
+          <t>8,49; 11,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,32</t>
+          <t>7,91; 10,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,02</t>
+          <t>3,35; 8,23</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>8179</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9272</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2905</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8066</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1617</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4436; 12636</t>
+          <t>2627; 10566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5066; 14759</t>
+          <t>3864; 14726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>788; 6823</t>
+          <t>1827; 9952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 3195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2629; 10157</t>
+          <t>4558; 13476</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4179; 14712</t>
+          <t>5092; 14911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1663; 8844</t>
+          <t>746; 6847</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3090</t>
+          <t>0; 3504</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8384; 19832</t>
+          <t>8659; 20371</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11681; 24944</t>
+          <t>11412; 24941</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3645; 12973</t>
+          <t>3654; 12669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>365; 4727</t>
+          <t>353; 4327</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32907</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46922</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34652</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>26747</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>38620</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>48148</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32907</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46922</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34652</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>6998</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18701; 34823</t>
+          <t>25009; 41877</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30194; 49406</t>
+          <t>36721; 59931</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38697; 60335</t>
+          <t>25765; 45038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2184; 8412</t>
+          <t>1047; 5291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24420; 42836</t>
+          <t>19560; 36402</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37045; 59145</t>
+          <t>30242; 49634</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26433; 45283</t>
+          <t>38677; 59875</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1441; 6746</t>
+          <t>1847; 8327</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49086; 72388</t>
+          <t>48679; 71573</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72214; 101119</t>
+          <t>70971; 101742</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70277; 97956</t>
+          <t>69344; 99338</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4520; 13286</t>
+          <t>4121; 11817</t>
         </is>
       </c>
     </row>
@@ -1784,37 +1784,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13810</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15190</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19520</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>16201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>17216</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9195</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13810</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15190</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2771</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10704; 23419</t>
+          <t>8685; 20777</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11461; 24639</t>
+          <t>9959; 22030</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5129; 15485</t>
+          <t>13381; 28265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5991</t>
+          <t>0; 5008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8466; 20560</t>
+          <t>10509; 23602</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9419; 22256</t>
+          <t>11638; 25026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13428; 27209</t>
+          <t>5158; 14669</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4505</t>
+          <t>0; 5171</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22141; 39497</t>
+          <t>21758; 38849</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24008; 42763</t>
+          <t>24213; 42783</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20957; 37851</t>
+          <t>20694; 37247</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>933; 6777</t>
+          <t>868; 7751</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70178</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70178</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42169; 63698</t>
+          <t>41393; 62749</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53923; 77796</t>
+          <t>58653; 84041</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49014; 74082</t>
+          <t>45971; 72075</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3769; 12784</t>
+          <t>2282; 8806</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42429; 63941</t>
+          <t>40701; 62933</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58142; 83651</t>
+          <t>52968; 78747</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47953; 72760</t>
+          <t>49663; 72997</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2529; 10005</t>
+          <t>3298; 12315</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89537; 119611</t>
+          <t>88530; 119171</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117903; 153264</t>
+          <t>116415; 155394</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102758; 135141</t>
+          <t>103583; 137035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7716; 18602</t>
+          <t>7286; 17885</t>
         </is>
       </c>
     </row>
